--- a/data/trans_bre/IP28_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP28_R-Estudios-trans_bre.xlsx
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 2,53</t>
+          <t>-5,31; 2,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 6,27</t>
+          <t>-1,71; 6,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 3,43</t>
+          <t>-4,5; 3,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 0,0</t>
+          <t>-8,58; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 649,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 1,55</t>
+          <t>-0,83; 1,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 1,9</t>
+          <t>-1,05; 1,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 1,01</t>
+          <t>-1,15; 1,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 2,12</t>
+          <t>-0,47; 2,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-59,61; 269,72</t>
+          <t>-56,27; 272,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-50,19; 173,76</t>
+          <t>-46,62; 189,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-77,81; 194,92</t>
+          <t>-72,61; 198,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-45,2; 404,38</t>
+          <t>-40,95; 412,54</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 2,03</t>
+          <t>-0,81; 2,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 1,97</t>
+          <t>-2,14; 1,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 2,29</t>
+          <t>-0,37; 2,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 3,28</t>
+          <t>-0,7; 3,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 1,06</t>
+          <t>-0,78; 1,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 1,59</t>
+          <t>-0,93; 1,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -975,27 +975,27 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 1,7</t>
+          <t>-0,38; 1,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-55,4; 130,42</t>
+          <t>-49,39; 143,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-38,24; 152,14</t>
+          <t>-39,76; 133,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-64,61; 155,35</t>
+          <t>-65,23; 153,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-37,83; 316,47</t>
+          <t>-36,79; 288,3</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP28_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP28_R-Estudios-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su peso es bastante mayor de lo normal en relación con su altura</t>
+          <t>Menores cuyo peso es bastante mayor de lo normal en relación con su altura</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 2,42</t>
+          <t>-5,75; 2,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 6,02</t>
+          <t>-1,87; 6,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 3,88</t>
+          <t>-4,39; 4,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,58; 0,0</t>
+          <t>-6,83; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 649,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 1,52</t>
+          <t>-0,91; 1,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 1,99</t>
+          <t>-1,11; 2,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 1,01</t>
+          <t>-1,14; 1,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 2,09</t>
+          <t>-0,57; 2,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-56,27; 272,83</t>
+          <t>-60,22; 223,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-46,62; 189,04</t>
+          <t>-49,59; 185,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-72,61; 198,23</t>
+          <t>-75,26; 206,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-40,95; 412,54</t>
+          <t>-48,89; 379,31</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 2,29</t>
+          <t>-0,82; 2,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 1,62</t>
+          <t>-2,16; 1,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 2,39</t>
+          <t>-0,65; 2,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 3,41</t>
+          <t>-0,73; 3,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 1,09</t>
+          <t>-0,87; 1,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 1,55</t>
+          <t>-0,81; 1,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 0,84</t>
+          <t>-0,86; 0,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 1,66</t>
+          <t>-0,51; 1,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-49,39; 143,82</t>
+          <t>-53,85; 133,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-39,76; 133,44</t>
+          <t>-38,19; 140,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-65,23; 153,28</t>
+          <t>-62,57; 157,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-36,79; 288,3</t>
+          <t>-41,27; 281,31</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP28_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP28_R-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-2,17</t>
+          <t>-2,33</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 2,35</t>
+          <t>-5,64; 2,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 6,01</t>
+          <t>-1,77; 6,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 4,05</t>
+          <t>-4,49; 3,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 0,0</t>
+          <t>-9,26; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,69</t>
+          <t>0,93</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>90,77%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 1,5</t>
+          <t>-0,9; 1,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 2,08</t>
+          <t>-1,15; 1,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 1,04</t>
+          <t>-1,26; 1,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 2,13</t>
+          <t>-0,33; 2,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-60,22; 223,69</t>
+          <t>-59,61; 269,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-49,59; 185,29</t>
+          <t>-50,19; 173,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-75,26; 206,29</t>
+          <t>-77,81; 194,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-48,89; 379,31</t>
+          <t>-37,27; 441,01</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,67</t>
+          <t>0,71</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>142,17%</t>
+          <t>141,18%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 2,04</t>
+          <t>-0,81; 2,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 1,67</t>
+          <t>-2,15; 1,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 2,21</t>
+          <t>-0,38; 2,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 3,31</t>
+          <t>-0,58; 3,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>0,63</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>62,22%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 1,03</t>
+          <t>-0,88; 1,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 1,6</t>
+          <t>-0,83; 1,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 0,85</t>
+          <t>-0,95; 0,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 1,59</t>
+          <t>-0,38; 1,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-53,85; 133,07</t>
+          <t>-55,4; 130,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-38,19; 140,22</t>
+          <t>-38,24; 152,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-62,57; 157,67</t>
+          <t>-64,61; 155,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-41,27; 281,31</t>
+          <t>-32,44; 360,68</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP28_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP28_R-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -522,7 +531,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores cuyo peso es bastante mayor de lo normal en relación con su altura</t>
+          <t>Menores cuya percepción de los madres/padres es que su peso es bastante mayor de lo normal en relación con su altura</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -610,299 +619,183 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-1,39</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1,74</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,69</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-2,33</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-43,23%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>105,19%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-31,54%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-1.385499392184712</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>1.735933902608513</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-0.6874303154737903</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-2.328076963447156</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.4323159867198746</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>1.051939482983742</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.3153647465256426</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-5,64; 2,53</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-1,77; 6,27</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-4,49; 3,43</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-9,26; 0,0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-5.641533703494252</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-1.770329456468805</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-4.488273847418306</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-9.259664140742913</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>2.52953208671425</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>6.274970188001924</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>3.432138245137991</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,27</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,34</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,07</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,93</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>23,45%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>18,95%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-6,74%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>90,77%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-0,9; 1,55</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-1,15; 1,9</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-1,26; 1,01</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-0,33; 2,53</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-59,61; 269,72</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-50,19; 173,76</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-77,81; 194,92</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-37,27; 441,01</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.2687877643280986</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.3401194014644112</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.07262636973451811</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0.9334447459056686</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.2345145697796948</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.189547804544009</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.06744631628870883</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.9076879407858606</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,41</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,31</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,49</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,71</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,02%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-23,74%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>131,32%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>141,18%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-0.8965789901269984</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-1.148946312964082</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-1.262871279631062</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-0.3313236062658256</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.5961192537267427</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.5019467401310219</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.7780796700172776</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.372669868477119</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-0,81; 2,03</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-2,15; 1,97</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-0,38; 2,29</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-0,58; 3,45</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1.552989378369823</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1.90383324226615</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1.006504166839011</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>2.528794668589624</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>2.697212615963631</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1.737551258240616</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>1.94922050054287</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>4.410129440541857</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,97 +803,181 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,08</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,36</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,01</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,63</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6,88%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>21,79%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>62,22%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>0.4073143319778333</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.3057236666662258</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.4857743539210207</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.7117047961224895</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>1.000217120699822</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.2374400239597303</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>1.313231107314396</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>1.411842024973291</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-0,88; 1,06</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-0,83; 1,59</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-0,95; 0,84</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-0,38; 1,93</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-55,4; 130,42</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-38,24; 152,14</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-64,61; 155,35</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-32,44; 360,68</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-0.8122906936512359</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-2.145760072227435</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-0.3751106942056063</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-0.5795493330161933</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>2.034148321405969</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1.969969498522302</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2.290345148352708</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>3.452922226579801</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.08474166898147749</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.3612330515423343</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.008143490196063467</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0.6276267526649303</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.06876027409908927</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.2178621480883994</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.008158841536641696</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.6222419302275433</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-0.883090482462823</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-0.8251975883277939</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-0.9535373450124738</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-0.3799131699294249</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.5540119800938642</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.382444498779656</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.6460666327854516</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.324378350180249</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1.059740012425532</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1.594630486244709</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.8362450533843127</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>1.933357390579922</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>1.304164570238028</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1.521389621394318</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>1.553455108856382</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>3.6068142561542</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1008,13 +985,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
